--- a/yolo11_pose_run-batch4/訓練摘要.xlsx
+++ b/yolo11_pose_run-batch4/訓練摘要.xlsx
@@ -476,28 +476,28 @@
         <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>0.973</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9388</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9746</v>
+        <v>0.9766</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7229</v>
+        <v>0.7625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.973</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9388</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9784</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9657</v>
+        <v>0.9743000000000001</v>
       </c>
     </row>
   </sheetData>
